--- a/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
+++ b/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
@@ -46,7 +46,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +96,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -459,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -469,8 +476,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,231 +493,161 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Super intensivo (20h/sem): max 5 cuotas. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REGLA: el estudiante termina de PAGAR antes de terminar el programa - por eso cada modalidad tiene su maximo de cuotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TRANSFORMACION  -  Beca del Fondo: contado 45% / cuotas 36%</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>4782800</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>5565440</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~7 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>5 cuotas</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>6 cuotas</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>8 cuotas</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>10 cuotas</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>11 cuotas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>20% = $1.113.088</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B10" s="12" t="n">
         <v>1540868</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C10" s="12" t="n">
         <v>1166457</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="12" t="n">
         <v>941864</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>792179</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>605173</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>493075</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>452348</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>30% = $1.669.632</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>1348259</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C11" s="12" t="n">
         <v>1020650</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="12" t="n">
         <v>824131</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>693157</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>529526</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>431441</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>395805</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>40% = $2.226.176</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B12" s="12" t="n">
         <v>1155651</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C12" s="12" t="n">
         <v>874843</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="12" t="n">
         <v>706398</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>594135</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>453880</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>369806</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>339261</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>50% = $2.782.720</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>963042</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C13" s="12" t="n">
         <v>729036</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D13" s="12" t="n">
         <v>588665</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>495112</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>378233</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>308172</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>282718</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL  -  Beca del Fondo: contado 32% / cuotas 25.6%</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO CONTADO</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5913280</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO BASE A CUOTAS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>6469824</v>
-      </c>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~14 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -720,158 +655,124 @@
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>3 cuotas</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>5 cuotas</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>10 cuotas</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>11 cuotas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>20% = $1.293.965</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>1791259</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>1356006</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>1094917</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>920909</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>703514</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>573200</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>525855</v>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.113.088</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1166457</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>792179</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>605173</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>493075</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>452348</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>30% = $1.940.947</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1567351</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>1186506</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>958052</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>805795</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>615574</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>501550</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>460123</v>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.669.632</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>1020650</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>693157</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>529526</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>431441</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>395805</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>40% = $2.587.930</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>1343444</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>1017005</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>821188</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>690681</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>527635</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>429900</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>394391</v>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.226.176</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>874843</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>594135</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>453880</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>369806</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>339261</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>50% = $3.234.912</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>1119537</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>847504</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>684323</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>575568</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>439696</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>358250</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>328659</v>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.782.720</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>729036</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>495112</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>378233</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>308172</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>282718</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>EJECUTIVO  -  Beca del Fondo: contado 15% / cuotas 12%</t>
+          <t>GENERAL  -  Beca del Fondo: contado 32% / cuotas 25.6%</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -880,8 +781,6 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -890,168 +789,509 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
+        <v>5913280</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO BASE A CUOTAS</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>6469824</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~7 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>3 cuotas</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>5 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.293.965</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1791259</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1356006</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>1094917</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.940.947</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1567351</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1186506</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>958052</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.587.930</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>1343444</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>1017005</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>821188</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>50% = $3.234.912</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>1119537</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>847504</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>684323</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~14 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>6 cuotas</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>8 cuotas</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>10 cuotas</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>11 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.293.965</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>1356006</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>920909</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>703514</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>573200</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>525855</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.940.947</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>1186506</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>805795</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>615574</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>501550</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>460123</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.587.930</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>1017005</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>690681</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>527635</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>429900</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>394391</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>50% = $3.234.912</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>847504</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>575568</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>439696</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>358250</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>328659</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EJECUTIVO  -  Beca del Fondo: contado 15% / cuotas 12%</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO CONTADO</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
         <v>7391600</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E37" s="7" t="n">
         <v>7652480</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~7 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>5 cuotas</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.530.496</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>2118693</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1603879</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1295063</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>30% = $2.295.744</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>1853856</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1403394</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>1133180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>40% = $3.060.992</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1589020</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1202909</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>971297</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>50% = $3.826.240</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>1324183</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>1002424</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>809414</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~14 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>10 cuotas</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>11 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>20% = $1.530.496</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>2118693</v>
-      </c>
-      <c r="C24" s="10" t="n">
+      <c r="B46" s="12" t="n">
         <v>1603879</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>1295063</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>1089247</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>832113</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>677978</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>621979</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>30% = $2.295.744</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>1853856</v>
-      </c>
-      <c r="C25" s="10" t="n">
+      <c r="B47" s="12" t="n">
         <v>1403394</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>1133180</v>
-      </c>
-      <c r="E25" s="10" t="n">
+      <c r="C47" s="12" t="n">
         <v>953091</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="D47" s="12" t="n">
         <v>728099</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="E47" s="12" t="n">
         <v>593231</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="F47" s="12" t="n">
         <v>544232</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>40% = $3.060.992</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>1589020</v>
-      </c>
-      <c r="C26" s="10" t="n">
+      <c r="B48" s="12" t="n">
         <v>1202909</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>971297</v>
-      </c>
-      <c r="E26" s="10" t="n">
+      <c r="C48" s="12" t="n">
         <v>816935</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="D48" s="12" t="n">
         <v>624085</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="E48" s="12" t="n">
         <v>508484</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="F48" s="12" t="n">
         <v>466484</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>50% = $3.826.240</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>1324183</v>
-      </c>
-      <c r="C27" s="10" t="n">
+      <c r="B49" s="12" t="n">
         <v>1002424</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>809414</v>
-      </c>
-      <c r="E27" s="10" t="n">
+      <c r="C49" s="12" t="n">
         <v>680779</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="D49" s="12" t="n">
         <v>520071</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="E49" s="12" t="n">
         <v>423736</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="F49" s="12" t="n">
         <v>388737</v>
       </c>
     </row>
@@ -1066,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1076,8 +1316,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1095,231 +1333,161 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Super intensivo (20h/sem): max 5 cuotas. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REGLA: el estudiante termina de PAGAR antes de terminar el programa - por eso cada modalidad tiene su maximo de cuotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TRANSFORMACION  -  Beca del Fondo: contado 36% / cuotas 27%</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>4544000</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>5183000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~6 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>5 cuotas</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>6 cuotas</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>8 cuotas</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>10 cuotas</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>11 cuotas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>20% = $1.036.600</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B10" s="12" t="n">
         <v>1434984</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C10" s="12" t="n">
         <v>1086302</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="12" t="n">
         <v>877142</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>737743</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>563587</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>459192</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>421264</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>30% = $1.554.900</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>1255611</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C11" s="12" t="n">
         <v>950514</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="12" t="n">
         <v>767499</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>645525</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>493139</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>401793</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>368606</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>40% = $2.073.200</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B12" s="12" t="n">
         <v>1076238</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C12" s="12" t="n">
         <v>814726</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="12" t="n">
         <v>657856</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>553307</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>422691</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>344394</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>315948</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>50% = $2.591.500</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>896865</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C13" s="12" t="n">
         <v>678939</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D13" s="12" t="n">
         <v>548214</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>461090</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>352242</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>286995</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>263290</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL  -  Beca del Fondo: contado 25.6% / cuotas 19.2%</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO CONTADO</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5282400</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO BASE A CUOTAS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>5736800</v>
-      </c>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~12 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1327,158 +1495,124 @@
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>3 cuotas</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>5 cuotas</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>10 cuotas</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>11 cuotas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>20% = $1.147.360</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>1588311</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>1202372</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>970864</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>816571</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>623806</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>508257</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>466276</v>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.036.600</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1086302</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>737743</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>563587</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>459192</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>421264</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>30% = $1.721.040</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1389772</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>1052076</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>849506</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>714499</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>545831</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>444725</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>407992</v>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.554.900</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>950514</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>645525</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>493139</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>401793</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>368606</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>40% = $2.294.720</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>1191233</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>901779</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>728148</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>612428</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>467855</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>381193</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>349707</v>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.073.200</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>814726</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>553307</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>422691</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>344394</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>315948</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>50% = $2.868.400</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>992694</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>751483</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>606790</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>510357</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>389879</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>317661</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>291423</v>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.591.500</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>678939</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>461090</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>352242</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>286995</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>263290</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>EJECUTIVO  -  Beca del Fondo: contado 12% / cuotas 9%</t>
+          <t>GENERAL  -  Beca del Fondo: contado 25.6% / cuotas 19.2%</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1487,8 +1621,6 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1497,168 +1629,509 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
+        <v>5282400</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO BASE A CUOTAS</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>5736800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~6 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>3 cuotas</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>5 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.147.360</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1588311</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1202372</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>970864</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.721.040</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1389772</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1052076</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>849506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.294.720</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>1191233</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>901779</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>728148</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.868.400</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>992694</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>751483</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>606790</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~12 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>6 cuotas</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>8 cuotas</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>10 cuotas</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>11 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.147.360</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>1202372</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>816571</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>623806</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>508257</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>466276</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.721.040</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>1052076</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>714499</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>545831</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>444725</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>407992</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.294.720</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>901779</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>612428</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>467855</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>381193</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>349707</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.868.400</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>751483</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>510357</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>389879</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>317661</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>291423</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EJECUTIVO  -  Beca del Fondo: contado 12% / cuotas 9%</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO CONTADO</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
         <v>6248000</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E37" s="7" t="n">
         <v>6461000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~6 meses - MAX 5 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>5 cuotas</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>20% = $1.292.200</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>1788816</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1354157</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1093424</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.938.300</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>1565214</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1184887</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>956746</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>40% = $2.584.400</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1341612</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1015618</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>820068</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>50% = $3.230.500</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>1118010</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>846348</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>683390</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~12 meses - MAX 11 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>10 cuotas</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>11 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>20% = $1.292.200</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>1788816</v>
-      </c>
-      <c r="C24" s="10" t="n">
+      <c r="B46" s="12" t="n">
         <v>1354157</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>1093424</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>919653</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>702554</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>572418</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>525138</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>30% = $1.938.300</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>1565214</v>
-      </c>
-      <c r="C25" s="10" t="n">
+      <c r="B47" s="12" t="n">
         <v>1184887</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>956746</v>
-      </c>
-      <c r="E25" s="10" t="n">
+      <c r="C47" s="12" t="n">
         <v>804696</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="D47" s="12" t="n">
         <v>614735</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="E47" s="12" t="n">
         <v>500866</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="F47" s="12" t="n">
         <v>459495</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>40% = $2.584.400</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>1341612</v>
-      </c>
-      <c r="C26" s="10" t="n">
+      <c r="B48" s="12" t="n">
         <v>1015618</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>820068</v>
-      </c>
-      <c r="E26" s="10" t="n">
+      <c r="C48" s="12" t="n">
         <v>689739</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="D48" s="12" t="n">
         <v>526916</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="E48" s="12" t="n">
         <v>429314</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="F48" s="12" t="n">
         <v>393853</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>50% = $3.230.500</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>1118010</v>
-      </c>
-      <c r="C27" s="10" t="n">
+      <c r="B49" s="12" t="n">
         <v>846348</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>683390</v>
-      </c>
-      <c r="E27" s="10" t="n">
+      <c r="C49" s="12" t="n">
         <v>574783</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="D49" s="12" t="n">
         <v>439096</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="E49" s="12" t="n">
         <v>357761</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="F49" s="12" t="n">
         <v>328211</v>
       </c>
     </row>
@@ -1673,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1683,8 +2156,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1702,193 +2173,144 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Super intensivo (20h/sem): max 3 cuotas. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REGLA: el estudiante termina de PAGAR antes de terminar el programa - por eso cada modalidad tiene su maximo de cuotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TRANSFORMACION  -  Beca del Fondo: contado 24.8% / cuotas 15.8%</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>3899120</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>4365770</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~4,5 meses - MAX 3 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2 cuotas</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>4 cuotas</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>6 cuotas</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>8 cuotas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>20% = $873.154</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B10" s="12" t="n">
         <v>1796234</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C10" s="12" t="n">
         <v>1208723</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>915019</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>621420</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>474724</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>30% = $1.309.731</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>1571705</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C11" s="12" t="n">
         <v>1057632</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>800642</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>543742</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>415383</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>40% = $1.746.308</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B12" s="12" t="n">
         <v>1347175</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C12" s="12" t="n">
         <v>906542</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>686264</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>466065</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>356043</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>50% = $2.182.885</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>1122646</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C13" s="12" t="n">
         <v>755452</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>571887</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>388387</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>296702</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL  -  Beca del Fondo: contado 17.6% / cuotas 11.2%</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO CONTADO</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>4272440</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PRECIO BASE A CUOTAS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>4604280</v>
-      </c>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~9 meses - MAX 8 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1896,124 +2318,90 @@
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>2 cuotas</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>3 cuotas</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>20% = $920.856</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>1894365</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>1274757</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>965008</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>655369</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>500659</v>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>20% = $873.154</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>915019</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>621420</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>474724</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>30% = $1.381.284</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1657570</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>1115413</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>844382</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>573448</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>438076</v>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.309.731</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>800642</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>543742</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>415383</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>40% = $1.841.712</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>1420774</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>956068</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>723756</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>491527</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>375494</v>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>40% = $1.746.308</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>686264</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>466065</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>356043</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>50% = $2.302.140</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>1183978</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>796723</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>603130</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>409606</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>312912</v>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.182.885</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>571887</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>388387</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>296702</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>EJECUTIVO  -  Beca del Fondo: contado 8.3% / cuotas 5.3%</t>
+          <t>GENERAL  -  Beca del Fondo: contado 17.6% / cuotas 11.2%</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -2030,134 +2418,407 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
+        <v>4272440</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO BASE A CUOTAS</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>4604280</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~4,5 meses - MAX 3 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>2 cuotas</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>3 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>20% = $920.856</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1894365</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1274757</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.381.284</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1657570</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1115413</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>40% = $1.841.712</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>1420774</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>956068</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.302.140</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>1183978</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>796723</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~9 meses - MAX 8 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>6 cuotas</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>8 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>20% = $920.856</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>965008</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>655369</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>500659</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.381.284</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>844382</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>573448</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>438076</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>40% = $1.841.712</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>723756</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>491527</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>375494</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.302.140</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>603130</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>409606</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>312912</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EJECUTIVO  -  Beca del Fondo: contado 8.3% / cuotas 5.3%</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>PRECIO CONTADO</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
         <v>4754645</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E37" s="7" t="n">
         <v>4910195</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>SUPER INTENSIVO 20h/sem - ~4,5 meses - MAX 3 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>2 cuotas</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>20% = $982.039</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>2020230</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1359454</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>30% = $1.473.058</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>1767701</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1189523</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>40% = $1.964.078</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1515172</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1019591</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>50% = $2.455.098</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>1262643</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>849659</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~9 meses - MAX 8 CUOTAS</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>6 cuotas</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>8 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>20% = $982.039</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>2020230</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>1359454</v>
-      </c>
-      <c r="D24" s="10" t="n">
+      <c r="B46" s="12" t="n">
         <v>1029125</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>698912</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>533923</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>30% = $1.473.058</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>1767701</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>1189523</v>
-      </c>
-      <c r="D25" s="10" t="n">
+      <c r="B47" s="12" t="n">
         <v>900484</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="C47" s="12" t="n">
         <v>611548</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="D47" s="12" t="n">
         <v>467183</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>40% = $1.964.078</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>1515172</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>1019591</v>
-      </c>
-      <c r="D26" s="10" t="n">
+      <c r="B48" s="12" t="n">
         <v>771844</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="C48" s="12" t="n">
         <v>524184</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="D48" s="12" t="n">
         <v>400442</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>50% = $2.455.098</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>1262643</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>849659</v>
-      </c>
-      <c r="D27" s="10" t="n">
+      <c r="B49" s="12" t="n">
         <v>643203</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="C49" s="12" t="n">
         <v>436820</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="D49" s="12" t="n">
         <v>333702</v>
       </c>
     </row>
@@ -2172,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2182,8 +2843,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2201,354 +2860,406 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Super intensivo (20h/sem): max 4 cuotas. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REGLA: el estudiante termina de PAGAR antes de terminar el programa - por eso cada modalidad tiene su maximo de cuotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TRANSFORMACION  -  Beca del Fondo: contado 20.3% / cuotas 11.3%</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>1867371</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>2078241</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~5 meses - MAX 4 CUOTAS (en super intensivo dura ~2,5 meses: practicamente contado)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2 cuotas</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>20% = $415.648</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B10" s="12" t="n">
         <v>855063</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C10" s="12" t="n">
         <v>575389</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="12" t="n">
         <v>435577</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>30% = $623.472</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>748180</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C11" s="12" t="n">
         <v>503466</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="12" t="n">
         <v>381130</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>40% = $831.296</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B12" s="12" t="n">
         <v>641297</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C12" s="12" t="n">
         <v>431542</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="12" t="n">
         <v>326683</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>50% = $1.039.120</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>534414</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C13" s="12" t="n">
         <v>359618</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D13" s="12" t="n">
         <v>272236</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GENERAL  -  Beca del Fondo: contado 14.4% / cuotas 8%</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B16" s="7" t="n">
         <v>2005608</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>2155560</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~5 meses - MAX 4 CUOTAS (en super intensivo dura ~2,5 meses: practicamente contado)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>2 cuotas</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>20% = $431.112</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B19" s="12" t="n">
         <v>886874</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C19" s="12" t="n">
         <v>596796</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D19" s="12" t="n">
         <v>451783</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>30% = $646.668</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B20" s="12" t="n">
         <v>776015</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C20" s="12" t="n">
         <v>522197</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D20" s="12" t="n">
         <v>395310</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>40% = $862.224</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B21" s="12" t="n">
         <v>665156</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C21" s="12" t="n">
         <v>447597</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D21" s="12" t="n">
         <v>338837</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>50% = $1.077.780</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B22" s="12" t="n">
         <v>554297</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C22" s="12" t="n">
         <v>372998</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D22" s="12" t="n">
         <v>282364</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>EJECUTIVO  -  Beca del Fondo: contado 6.8% / cuotas 3.8%</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>PRECIO CONTADO</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B25" s="7" t="n">
         <v>2183676</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>PRECIO BASE A CUOTAS</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E25" s="7" t="n">
         <v>2253966</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>INTENSIVO 10h/sem - ~5 meses - MAX 4 CUOTAS (en super intensivo dura ~2,5 meses: practicamente contado)</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Cuota inicial</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>2 cuotas</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>3 cuotas</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>4 cuotas</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>20% = $450.793</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B28" s="12" t="n">
         <v>927362</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C28" s="12" t="n">
         <v>624041</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D28" s="12" t="n">
         <v>472407</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>30% = $676.190</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B29" s="12" t="n">
         <v>811442</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C29" s="12" t="n">
         <v>546036</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D29" s="12" t="n">
         <v>413356</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>40% = $901.586</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B30" s="12" t="n">
         <v>695522</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C30" s="12" t="n">
         <v>468031</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D30" s="12" t="n">
         <v>354306</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>50% = $1.126.983</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B31" s="12" t="n">
         <v>579601</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C31" s="12" t="n">
         <v>390026</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D31" s="12" t="n">
         <v>295255</v>
       </c>
     </row>

--- a/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
+++ b/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A2-B2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1-B2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solo B2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARRANQUE A1+A2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +503,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+          <t>Separacion de cupo $300.000 (se cruza con la inicial) -&gt; cuota inicial min 20% max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1343,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+          <t>Separacion de cupo $300.000 (se cruza con la inicial) -&gt; cuota inicial min 20% max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2183,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+          <t>Separacion de cupo $300.000 (se cruza con la inicial) -&gt; cuota inicial min 20% max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2870,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Reserva $100-150 mil dia 1 -&gt; cuota inicial max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+          <t>Separacion de cupo $300.000 (se cruza con la inicial) -&gt; cuota inicial min 20% max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
         </is>
       </c>
     </row>
@@ -3266,4 +3267,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HEIIU - MOTOR DE CUOTAS 2026 - USO INTERNO (jamas mostrar al cliente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ARRANQUE A1+A2 - PRECIO UNICO DE LANZAMIENTO: $2.990.000 (200 horas) - SIN BECAS - Interes credito directo: 1,9% mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REGLA: se termina de pagar antes de terminar. Super intensivo 20h/sem ~2,5 meses: MAX 2 CUOTAS. Intensivo 10h/sem ~5 meses: MAX 4 CUOTAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Separacion de cupo $300.000 (se cruza con la inicial) -&gt; cuota inicial min 20% max 3 dias -&gt; cuotas desde dia 30. Credito SIEMPRE con pagare + carta + plan de pagos firmados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PRECIO (contado o a cuotas): $2.990.000</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Cuota inicial</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2 cuotas</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>3 cuotas</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>4 cuotas</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>20% = $598.000</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>1230193</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>827822</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>626672</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Super intensivo: solo columna 2 cuotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>30% = $897.000</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1076419</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>724344</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>548338</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>40% = $1.196.000</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>922645</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>620867</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>470004</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>50% = $1.495.000</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>768871</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>517389</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>391670</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
+++ b/recursos/comercial/INDUCCION_COMERCIAL/MOTOR_CUOTAS_FONDO_2026.xlsx
@@ -507,10 +507,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TRANSFORMACION  -  Beca del Fondo: contado 45% / cuotas 36%</t>
+          <t>TRANSFORMACION (estrato 1-2 con soporte O AFILIADO A CAJASAN con carne)  -  Beca del Fondo: contado 45% / cuotas 36%</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -770,6 +771,7 @@
         <v>282718</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -1033,6 +1035,7 @@
         <v>328659</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -1347,10 +1350,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TRANSFORMACION  -  Beca del Fondo: contado 36% / cuotas 27%</t>
+          <t>TRANSFORMACION (estrato 1-2 con soporte O AFILIADO A CAJASAN con carne)  -  Beca del Fondo: contado 36% / cuotas 27%</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -1610,6 +1614,7 @@
         <v>263290</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -1873,6 +1878,7 @@
         <v>291423</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -2187,10 +2193,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TRANSFORMACION  -  Beca del Fondo: contado 24.8% / cuotas 15.8%</t>
+          <t>TRANSFORMACION (estrato 1-2 con soporte O AFILIADO A CAJASAN con carne)  -  Beca del Fondo: contado 24.8% / cuotas 15.8%</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -2399,6 +2406,7 @@
         <v>296702</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -2611,6 +2619,7 @@
         <v>312912</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -2874,10 +2883,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TRANSFORMACION  -  Beca del Fondo: contado 20.3% / cuotas 11.3%</t>
+          <t>TRANSFORMACION (estrato 1-2 con soporte O AFILIADO A CAJASAN con carne)  -  Beca del Fondo: contado 20.3% / cuotas 11.3%</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -3004,6 +3014,7 @@
         <v>272236</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -3134,6 +3145,7 @@
         <v>282364</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -3295,7 +3307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ARRANQUE A1+A2 - PRECIO UNICO DE LANZAMIENTO: $2.990.000 (200 horas) - SIN BECAS - Interes credito directo: 1,9% mensual</t>
+          <t>ARRANQUE A1+A2 - PRECIO UNICO DE LANZAMIENTO: $2.990.000 (200 horas) - SIN BECAS - Interes credito directo: 1,9% mensual - Afiliado Cajasan: mismo precio, sin beca</t>
         </is>
       </c>
     </row>
@@ -3313,6 +3325,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
